--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -34,8 +34,11 @@
     <sheet name="SERIES" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="CLUBS" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="META" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="TODO" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -43,7 +46,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +61,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +88,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +116,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18541,7 +18559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18949,6 +18967,47 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1951_52_0131 'Sokol Senec' ROZBITÝ prev CLUB_S1949_50_0472 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1951_52_0400 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0009</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1951_52_0009 'Mistrovství Slovenska' (L15, parent=NODE_S1951_52_0006) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -21535,8 +21594,6 @@
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -21604,7 +21661,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -43286,6 +43342,127 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0131</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0131 'Sokol Senec' ROZBITÝ prev CLUB_S1949_50_0472 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0400</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0400 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0009</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1951_52_0009 'Mistrovství Slovenska' (L15, parent=NODE_S1951_52_0006) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -37,7 +37,7 @@
     <sheet name="TODO" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18559,7 +18559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18973,7 +18973,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1951_52_0131 'Sokol Senec' ROZBITÝ prev CLUB_S1949_50_0472 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (Tatra Smíchov ← OD Praha). prev z 50/51 CLUB_S1950_51_0007. Vyžaduje verifikaci primárním zdrojem.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18985,7 +18985,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1951_52_0400 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ne) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: parentéze obsahuje historickou identitu (Tatra Kolín ← Sokol Kara Kolín). prev z 50/51 CLUB_S1950_51_0032. Vyžaduje verifikaci.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18995,17 +18995,180 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NODE_S1951_52_0009</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1951_52_0009 'Mistrovství Slovenska' (L15, parent=NODE_S1951_52_0006) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: Identity transition z 50/51 „Sokol Brandýs nad Labem" (CLUB_S1950_51_0155) na „Spartak Agrostroj Brandýs nad Labem" (51/52). V 51/52 ještě dominuje ZSJ-éra; přejmenování typu Sokol → Spartak je v této sezóně VÝJIMEČNÉ (plošný přechod přijde později). Pojmenování dle závodu Agrostroj Brandýs. Vyžaduje verifikaci primárním zdrojem.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: napojení na A-tým k ověření (LZ Plzeň mohlo být patrně přejmenování ze Škoda Plzeň).</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pošta Karlovy Vary' → 'Karlovy Vary' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0487 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centrofol Dolní Poustevna' → 'Dolní Poustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21594,6 +21757,8 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -21624,6 +21789,11 @@
           <t>Kvalifikace o MR (turnaje KP vítězů + SVK + baráž)</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0001</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21636,6 +21806,11 @@
           <t>Krajské přebory</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0001</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21648,6 +21823,11 @@
           <t>Kvalifikace o KP (kde existuje)</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0015</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21661,6 +21841,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -25055,12 +25236,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>České Budějovice = HC Motor České Budějovice (Wiki D42 - registr ustavy 04/2026). Vsechny ceskobudějovicke kluby. Hlavni chain: AC Stadion ČB -&gt; Slavoj ČB -&gt; TJ Motor ČB (1965+, podnik Motor) -&gt; HC Motor ČB. Plus paralelni: DA České Budějovice (Doprava arm), PDA II. ČB (poucovatelska), ZSJ Slavia ČB. city České Budějovice.</t>
+          <t>České Budějovice = HC Motor České Budějovice (Wiki D42 - registr ustavy 04/2026). Vsechny ceskobudějovicke kluby. Hlavni chain: AC Stadion ČB -&gt; Slavoj ČB -&gt; TJ Motor ČB (1965+, podnik Motor) -&gt; HC Motor ČB. Plus paralelni: DA České Budějovice (Doprava arm), PDA II. ČB (poucovatelska), ZSJ Slavia ČB. city České Budějovice. || TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Budvar České Budějovice</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29152,12 +29333,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Slavia KV (1932) -&gt; Sokol -&gt; Slovan -&gt; Spartak Slavia KV -&gt; Lokomotiva KV -&gt; RH Karlovy Vary (Ruda hvezda) -&gt; Energie KV. KV se 1949 jmenovaly Karlovy Vary, predtim Karlovy Vary/Karlsbad. city Karlovy Vary.</t>
+          <t>Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Slavia KV (1932) -&gt; Sokol -&gt; Slovan -&gt; Spartak Slavia KV -&gt; Lokomotiva KV -&gt; RH Karlovy Vary (Ruda hvezda) -&gt; Energie KV. KV se 1949 jmenovaly Karlovy Vary, predtim Karlovy Vary/Karlsbad. city Karlovy Vary. || TBD: city 'Pošta Karlovy Vary' → 'Karlovy Vary' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Pošta Karlovy Vary</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
     </row>
@@ -34178,9 +34359,14 @@
           <t>CLUB_S1950_51_0623</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>TBD: city 'Centrofol Dolní Poustevna' → 'Dolní Poustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Centrofol Dolní Poustevna</t>
+          <t>Dolní Poustevna</t>
         </is>
       </c>
     </row>
@@ -36326,12 +36512,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Oprava city: „RDP Svobodné Dvory" → „Svobodné Dvory". ZSJ RDP Svobodné Dvory → city ponechán „Svobodné Dvory" (Pavlova srdcovka — tam přesně ví). || ZSJ RDP Svobodné Dvory 51/52 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové.</t>
+          <t>Oprava city: „RDP Svobodné Dvory" → „Svobodné Dvory". ZSJ RDP Svobodné Dvory → city ponechán „Svobodné Dvory" (Pavlova srdcovka — tam přesně ví). || ZSJ RDP Svobodné Dvory 51/52 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové. || TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Svobodné Dvory</t>
         </is>
       </c>
     </row>
@@ -41449,12 +41635,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -42092,9 +42278,14 @@
           <t>Orlová</t>
         </is>
       </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Gottwald H. Suchá</t>
+          <t>Suchá</t>
         </is>
       </c>
     </row>
@@ -42356,12 +42547,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -42687,12 +42878,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -43352,11 +43543,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -43401,21 +43592,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0131</t>
+          <t>CLUB_S1951_52_0008</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0131 'Sokol Senec' ROZBITÝ prev CLUB_S1949_50_0472 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD-IDENTITY: V clean_name historická identita v parentézi (Tatra Smíchov ← OD Praha). prev z 50/51 CLUB_S1950_51_0007. Vyžaduje verifikaci primárním zdrojem.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -43423,21 +43612,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0400</t>
+          <t>CLUB_S1951_52_0042</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0400 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ne) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD-IDENTITY: parentéze obsahuje historickou identitu (Tatra Kolín ← Sokol Kara Kolín). prev z 50/51 CLUB_S1950_51_0032. Vyžaduje verifikaci.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -43445,24 +43632,302 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1951_52_0009</t>
+          <t>CLUB_S1951_52_0057</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1951_52_0009 'Mistrovství Slovenska' (L15, parent=NODE_S1951_52_0006) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD-IDENTITY: Identity transition z 50/51 „Sokol Brandýs nad Labem" (CLUB_S1950_51_0155) na „Spartak Agrostroj Brandýs nad Labem" (51/52). V 51/52 ještě dominuje ZSJ-éra; přejmenování typu Sokol → Spartak je v této sezóně VÝJIMEČNÉ (plošný přechod přijde později). Pojmenování dle závodu Agrostroj Brandýs. Vyžaduje verifikaci primárním zdrojem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0072</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0101</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>TBD: napojení na A-tým k ověření (LZ Plzeň mohlo být patrně přejmenování ze Škoda Plzeň).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0159</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Pošta Karlovy Vary' → 'Karlovy Vary' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0162</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0487 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0263</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Centrofol Dolní Poustevna' → 'Dolní Poustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0312</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0331</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0350</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0368</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0397</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0436</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0451</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0458</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1951_52_0466</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -37,7 +37,7 @@
     <sheet name="TODO" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18559,7 +18559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19069,7 +19069,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19081,7 +19081,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19093,7 +19093,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19105,7 +19105,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19117,7 +19117,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19129,7 +19129,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19141,7 +19141,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19153,22 +19153,10 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19185,7 +19173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19242,6 +19230,11 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
         </is>
       </c>
     </row>
@@ -36512,12 +36505,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Oprava city: „RDP Svobodné Dvory" → „Svobodné Dvory". ZSJ RDP Svobodné Dvory → city ponechán „Svobodné Dvory" (Pavlova srdcovka — tam přesně ví). || ZSJ RDP Svobodné Dvory 51/52 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové. || TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „RDP Svobodné Dvory" → „Svobodné Dvory". ZSJ RDP Svobodné Dvory → city ponechán „Svobodné Dvory" (Pavlova srdcovka — tam přesně ví). || ZSJ RDP Svobodné Dvory 51/52 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové.</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Svobodné Dvory</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -43543,7 +43536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -43757,12 +43750,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0312</t>
+          <t>CLUB_S1951_52_0331</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
         </is>
       </c>
     </row>
@@ -43777,12 +43770,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0331</t>
+          <t>CLUB_S1951_52_0350</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -43797,12 +43790,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0350</t>
+          <t>CLUB_S1951_52_0368</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43817,12 +43810,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0368</t>
+          <t>CLUB_S1951_52_0397</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
         </is>
       </c>
     </row>
@@ -43837,12 +43830,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0397</t>
+          <t>CLUB_S1951_52_0436</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43857,12 +43850,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0436</t>
+          <t>CLUB_S1951_52_0451</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43877,12 +43870,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0451</t>
+          <t>CLUB_S1951_52_0458</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43897,37 +43890,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1951_52_0458</t>
+          <t>CLUB_S1951_52_0466</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CLUB_S1951_52_0466</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F18"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
         <v>4</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M19" t="n">
         <v>18</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -19173,7 +19173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19237,6 +19237,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21750,8 +21760,6 @@
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -21834,7 +21842,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -19462,6 +19462,8 @@
           <t>NODE_S1951_52_0001</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19476,6 +19478,14 @@
         <is>
           <t>Top 2 z každé skupiny = 6 týmů</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -19759,11 +19769,8 @@
           <t>NODE_S1951_52_0009</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NODE_S1951_52_0013</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>home-away</t>
@@ -19778,6 +19785,14 @@
         <is>
           <t>BB vs Petržalka</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -19863,11 +19878,8 @@
           <t>NODE_S1951_52_0009</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>NODE_S1951_52_0014</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>home-away</t>
@@ -19882,6 +19894,14 @@
         <is>
           <t>Prešov vs Petržalka. Prešov vyhrál ale nepostoupil — místo něj Křídla vlasti Olomouc.</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -20229,6 +20249,8 @@
           <t>NODE_S1951_52_0015</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20238,6 +20260,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -21109,6 +21139,8 @@
           <t>NODE_S1951_52_0038</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21118,6 +21150,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -21760,6 +21800,8 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -21778,6 +21820,16 @@
           <t>Mistrovství republiky (3 sk. × 6 + finále)</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21842,6 +21894,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -957,11 +957,6 @@
           <t>SKP České Budějovice</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
@@ -2411,6 +2406,11 @@
       <c r="D26" t="inlineStr">
         <is>
           <t>Vítkovické Železárny</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -18559,7 +18559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19159,6 +19159,13 @@
       <c r="D34" t="inlineStr">
         <is>
           <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mistrovství republiky 1951/52: 3 skupiny po 6 → Finále mistrovství ČSR (2 nejlepší z každé skupiny). Mistr Vítkovice (před ATK Praha na skóre). Doloženo PDF i webem.</t>
         </is>
       </c>
     </row>
@@ -19462,8 +19469,6 @@
           <t>NODE_S1951_52_0001</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19769,8 +19774,6 @@
           <t>NODE_S1951_52_0009</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>home-away</t>
@@ -19878,8 +19881,6 @@
           <t>NODE_S1951_52_0009</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>home-away</t>
@@ -20249,8 +20250,6 @@
           <t>NODE_S1951_52_0015</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21139,8 +21138,6 @@
           <t>NODE_S1951_52_0038</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21800,8 +21797,6 @@
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -21820,8 +21815,6 @@
           <t>Mistrovství republiky (3 sk. × 6 + finále)</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>vítězové SF</t>
@@ -21894,7 +21887,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -43114,7 +43106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43281,7 +43273,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reorganizace pyramidy. Oblastní soutěže zrušeny. Liga 18 týmů ve 3 skupinách. Křídla vlasti Olomouc direktivně.</t>
+          <t>Mistr ZSJ Vítkovické železárny KG — vítěz Finále mistrovství ČSR (1., 8 b, lepší skóre než ATK Praha). Vůbec první titul Vítkovic. M badge opraven (byl chybně u SKP České Budějovice, který se do finále nedostal). Struktura: 3 základní skupiny po 6 → finále 6 (po 2 z každé skupiny).</t>
         </is>
       </c>
     </row>
@@ -43582,6 +43574,18 @@
       <c r="B39" t="inlineStr">
         <is>
           <t>Žilinský</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Vítkovické Železárny</t>
         </is>
       </c>
     </row>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -16066,10 +16066,10 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
         <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -16078,7 +16078,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -16086,10 +16086,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -16221,10 +16221,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
         <v>4</v>
@@ -18559,7 +18559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19166,6 +19166,34 @@
       <c r="A35" t="inlineStr">
         <is>
           <t>Mistrovství republiky 1951/52: 3 skupiny po 6 → Finále mistrovství ČSR (2 nejlepší z každé skupiny). Mistr Vítkovice (před ATK Praha na skóre). Doloženo PDF i webem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kvalifikace o Mistrovství republiky 1951/52 (turnaje krajských přeborníků): Skupina I (Holoubkov), Skupina II (OKD Ostrava), Skupina III = Mistrovství Slovenska (Dukla Prešov).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Vítěz slovenské skupiny (Dukla Prešov) nakonec do Mistrovství republiky NEpostoupil — místo něj byl po svém vzniku rovnou zařazen nový armádní tým Křídla vlasti Olomouc (odtud jeho původ v 1952/53 bez civilního předchůdce).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kvalifikace o Mistrovství republiky byla nakonec zbytečná: rozhodnuto, že nikdo nesestoupí a soutěž se rozšíří o vítěze kvalifikačních skupin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Krajské přebory 1951/52 (listy 20*) — bez externího zdroje (DS PDF pokrývá jen kvalifikaci + Mistrovství Slovenska), k ručnímu průchodu.</t>
         </is>
       </c>
     </row>

--- a/data/S1951_52_FINAL.xlsx
+++ b/data/S1951_52_FINAL.xlsx
@@ -18971,69 +18971,44 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (Tatra Smíchov ← OD Praha). prev z 50/51 CLUB_S1950_51_0007. Vyžaduje verifikaci primárním zdrojem.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mistrovství republiky 1951/52: 3 skupiny po 6 → Finále mistrovství ČSR (2 nejlepší z každé skupiny). Mistr Vítkovice (před ATK Praha na skóre). Doloženo PDF i webem.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: parentéze obsahuje historickou identitu (Tatra Kolín ← Sokol Kara Kolín). prev z 50/51 CLUB_S1950_51_0032. Vyžaduje verifikaci.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kvalifikace o Mistrovství republiky 1951/52 (turnaje krajských přeborníků): Skupina I (Holoubkov), Skupina II (OKD Ostrava), Skupina III = Mistrovství Slovenska (Dukla Prešov).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: Identity transition z 50/51 „Sokol Brandýs nad Labem" (CLUB_S1950_51_0155) na „Spartak Agrostroj Brandýs nad Labem" (51/52). V 51/52 ještě dominuje ZSJ-éra; přejmenování typu Sokol → Spartak je v této sezóně VÝJIMEČNÉ (plošný přechod přijde později). Pojmenování dle závodu Agrostroj Brandýs. Vyžaduje verifikaci primárním zdrojem.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vítěz slovenské skupiny (Dukla Prešov) nakonec do Mistrovství republiky NEpostoupil — místo něj byl po svém vzniku rovnou zařazen nový armádní tým Křídla vlasti Olomouc (odtud jeho původ v 1952/53 bez civilního předchůdce).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kvalifikace o Mistrovství republiky byla nakonec zbytečná: rozhodnuto, že nikdo nesestoupí a soutěž se rozšíří o vítěze kvalifikačních skupin.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: napojení na A-tým k ověření (LZ Plzeň mohlo být patrně přejmenování ze Škoda Plzeň).</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Krajské přebory 1951/52 (listy 20*) — bez externího zdroje (DS PDF pokrývá jen kvalifikaci + Mistrovství Slovenska), k ručnímu průchodu.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Pošta Karlovy Vary' → 'Karlovy Vary' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (Tatra Smíchov ← OD Praha). prev z 50/51 CLUB_S1950_51_0007. Vyžaduje verifikaci primárním zdrojem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19045,7 +19020,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0487 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: parentéze obsahuje historickou identitu (Tatra Kolín ← Sokol Kara Kolín). prev z 50/51 CLUB_S1950_51_0032. Vyžaduje verifikaci.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19057,7 +19032,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Centrofol Dolní Poustevna' → 'Dolní Poustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: Identity transition z 50/51 „Sokol Brandýs nad Labem" (CLUB_S1950_51_0155) na „Spartak Agrostroj Brandýs nad Labem" (51/52). V 51/52 ještě dominuje ZSJ-éra; přejmenování typu Sokol → Spartak je v této sezóně VÝJIMEČNÉ (plošný přechod přijde později). Pojmenování dle závodu Agrostroj Brandýs. Vyžaduje verifikaci primárním zdrojem.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19069,7 +19044,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19081,7 +19056,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: napojení na A-tým k ověření (LZ Plzeň mohlo být patrně přejmenování ze Škoda Plzeň).</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19093,7 +19068,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pošta Karlovy Vary' → 'Karlovy Vary' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19105,7 +19080,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0487 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19117,7 +19092,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centrofol Dolní Poustevna' → 'Dolní Poustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19129,7 +19104,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: kolegova nejistota o klubu, k ověření primárním zdrojem.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19141,7 +19116,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19153,47 +19128,72 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1950_51_0860 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: V clean_name historická identita v parentézi (BZGK ← OKD Horník Karviná). Bez prev. Vyžaduje verifikaci primárním zdrojem.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Mistrovství republiky 1951/52: 3 skupiny po 6 → Finále mistrovství ČSR (2 nejlepší z každé skupiny). Mistr Vítkovice (před ATK Praha na skóre). Doloženo PDF i webem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Kvalifikace o Mistrovství republiky 1951/52 (turnaje krajských přeborníků): Skupina I (Holoubkov), Skupina II (OKD Ostrava), Skupina III = Mistrovství Slovenska (Dukla Prešov).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Vítěz slovenské skupiny (Dukla Prešov) nakonec do Mistrovství republiky NEpostoupil — místo něj byl po svém vzniku rovnou zařazen nový armádní tým Křídla vlasti Olomouc (odtud jeho původ v 1952/53 bez civilního předchůdce).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Kvalifikace o Mistrovství republiky byla nakonec zbytečná: rozhodnuto, že nikdo nesestoupí a soutěž se rozšíří o vítěze kvalifikačních skupin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Krajské přebory 1951/52 (listy 20*) — bez externího zdroje (DS PDF pokrývá jen kvalifikaci + Mistrovství Slovenska), k ručnímu průchodu.</t>
         </is>
       </c>
     </row>
@@ -21825,6 +21825,8 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -21915,6 +21917,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
